--- a/shuju.xlsx
+++ b/shuju.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>通道</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,6 +75,14 @@
   </si>
   <si>
     <t>α</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拼孔值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EAFBGCDIH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -414,10 +422,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="12" max="12" width="14.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -481,7 +492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -513,7 +524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -545,60 +556,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="D5" s="1">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="E5" s="1">
-        <v>50</v>
+        <v>235</v>
       </c>
       <c r="F5" s="1">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="G5" s="1">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="I5" s="1">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="J5" s="1">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1">
+        <v>-67</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1">
         <v>80</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E7" s="1">
+        <v>168</v>
+      </c>
+      <c r="F7" s="1">
+        <v>-87</v>
+      </c>
+      <c r="G7" s="1">
+        <v>-56</v>
+      </c>
+      <c r="H7" s="1">
+        <v>34</v>
+      </c>
+      <c r="I7" s="1">
+        <v>193</v>
+      </c>
+      <c r="J7" s="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>90</v>
+      </c>
+      <c r="D9">
+        <v>148</v>
+      </c>
+      <c r="E9">
+        <v>232</v>
+      </c>
+      <c r="F9" s="1">
+        <v>-16</v>
+      </c>
+      <c r="G9" s="1">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1">
+        <v>117</v>
+      </c>
+      <c r="I9" s="1">
+        <v>270</v>
+      </c>
+      <c r="J9" s="1">
+        <v>256</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="11:11" x14ac:dyDescent="0.2">
@@ -630,6 +713,9 @@
     </row>
     <row r="26" spans="11:11" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
